--- a/fangzheng_web_app/default_rules/price_calculation/zhongjing/price_rules.xlsx
+++ b/fangzheng_web_app/default_rules/price_calculation/zhongjing/price_rules.xlsx
@@ -1,4596 +1,50 @@
 
-<file path=docProps\app.xml><?xml version="1.0" encoding="utf-8"?>
-<Properties xmlns="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <Application>Microsoft Excel</Application>
-  <HeadingPairs>
-    <vt:vector size="2" baseType="variant">
-      <vt:variant>
-        <vt:lpstr>工作表</vt:lpstr>
-      </vt:variant>
-      <vt:variant>
-        <vt:i4>8</vt:i4>
-      </vt:variant>
-    </vt:vector>
-  </HeadingPairs>
-  <TitlesOfParts>
-    <vt:vector size="8" baseType="lpstr">
-      <vt:lpstr>NY2170H</vt:lpstr>
-      <vt:lpstr>NY3170HF</vt:lpstr>
-      <vt:lpstr>NY3170M</vt:lpstr>
-      <vt:lpstr>NY3170M2</vt:lpstr>
-      <vt:lpstr>NY2150</vt:lpstr>
-      <vt:lpstr>NY3150HF</vt:lpstr>
-      <vt:lpstr>NY3176HF</vt:lpstr>
-      <vt:lpstr>NY6300SN</vt:lpstr>
-    </vt:vector>
-  </TitlesOfParts>
-</Properties>
+<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
+  <bookViews>
+    <workbookView windowWidth="20750" windowHeight="10270" activeTab="4"/>
+  </bookViews>
+  <sheets>
+    <sheet name="NY2170H" sheetId="13" r:id="rId1"/>
+    <sheet name="NY3170HF" sheetId="16" r:id="rId2"/>
+    <sheet name="NY3170M" sheetId="7" r:id="rId3"/>
+    <sheet name="NY3170M2" sheetId="8" r:id="rId4"/>
+    <sheet name="NY2150" sheetId="17" r:id="rId5"/>
+    <sheet name="NY3150HF" sheetId="18" r:id="rId6"/>
+    <sheet name="NY3176HF" sheetId="19" r:id="rId7"/>
+    <sheet name="NY6300SN" sheetId="20" r:id="rId8"/>
+  </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">NY2170H!$1:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">NY3170M!$1:$8</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">NY3170M2!$1:$9</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">NY2170H!$A$1:$L$75</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">NY3170M!$A$1:$L$112</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">NY3170HF!$1:$9</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">NY3170HF!$A$1:$L$83</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'NY2150'!$A$1:$K$69</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">NY3150HF!$A$1:$L$90</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
+</workbook>
 </file>
 
-<file path=docProps\core.xml><?xml version="1.0" encoding="utf-8"?>
-<cp:coreProperties xmlns:cp="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:dcmitype="http://purl.org/dc/dcmitype/" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
-  <cp:lastModifiedBy>陈艳</cp:lastModifiedBy>
-  <cp:revision>1</cp:revision>
-  <dcterms:created xsi:type="dcterms:W3CDTF">1996-12-17T01:32:00Z</dcterms:created>
-  <cp:lastPrinted>2026-01-08T05:59:00Z</cp:lastPrinted>
-  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-08-05T03:08:36Z</dcterms:modified>
-</cp:coreProperties>
-</file>
-
-<file path=docProps\custom.xml><?xml version="1.0" encoding="utf-8"?>
-<Properties xmlns="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <property fmtid="{D5CDD505-2E9C-101B-9397-08002B2CF9AE}" pid="2" name="KSOProductBuildVer">
-    <vt:lpwstr>2052-12.1.0.26895</vt:lpwstr>
-  </property>
-  <property fmtid="{D5CDD505-2E9C-101B-9397-08002B2CF9AE}" pid="3" name="ICV">
-    <vt:lpwstr>E53352A1D9D24ADA86F5D408BCB9D5A3_13</vt:lpwstr>
-  </property>
-  <property fmtid="{D5CDD505-2E9C-101B-9397-08002B2CF9AE}" pid="4" name="CalculationRule">
-    <vt:i4>0</vt:i4>
-  </property>
-  <property fmtid="{D5CDD505-2E9C-101B-9397-08002B2CF9AE}" pid="5" name="5B77E7CEEC58BC6AFAE8886BEB80DBEB">
-    <vt:lpwstr>otCYQxs9Dbw2bUEn/Soxv9pYAoWsCRIsU8+gIbxzzmNcJN13+qHIPyWmbF9hFzPHyi2m8DLwi54E5OVVM5pJ0yGmgAiYTaR6oYUdYZxdjep6I9xviFUFZ9aTScfBW9OGUdrWiVHdMdiGA8gq/F1fk4LoLkECXWUJQpglUNkXCBHRuesGJ+r65lcazm2As8k3DIMTaa2FRCJreJPpW53uDqqsNCQoI8qfxbM1FYTZFO+F0lI42kaut8t7XxXUOxvcTF1TJwuBZRfGiniYed3e7ejqKW/Di7UsowTGheJ99bsM1uqm7Fz41Ht7uhhgP0pRG9Rlk7bfS+6VyBc8juYKGjl4PhrUZFMYA+b5zTwkNoiwLJ9EbrQ1PKz2Aw+5QIDGO6FqHDX4MJRnLXkU6jUyKuAossyltHXtTeL9w73trmemL9wNRJA9edPsTQyHoK/2F2jt+pAHSaMsm8Cx7oL4bOp85kUARSE11yxMDaI7/80wzl/jFlt0uqLEfzzF6sCknlhh1esvwyKdDAHZr4TNb+mXZtL8i3l9StJnImw5VNC2M4GuKMMotbstbgJ+6vXRrhKRwAjL9kTGu74hzlpdumTSx5T5cqINqSK2E/p+xGSPM1HmahZO+FvrOKK/o8uVHflEz0Fkwu1r0CZL/pfA70MoBVXF4IjEctUc/6shSnVEVILfs/wbiy1EY8r0FDK8bxjf/s4HWVS6SdNmqP+A/SqO32VD0QurQQC7SQvmntAu+G4dRFyDoiKEnFl/sH6G5bMkdBH0i50z8oSrgvqkthxgu3enYWqO4ku9RutArE9xjfZGnubEjduZQTHt/DjeQ6ZClRz9E7jzuqPs3paINNAMk0ohVuztLkM9JYyiBamHm3TZ882Q4JDcgez7OPf6eLpAMVI5Y3O8MthK5U5y5u75ucNGANUMSgNEseXwoqgmbyHYr3y2eIfJVSVhPnoeSHuz6rrfg139fsITuYLovr5xSaCcwsOt4oAekHLLgdXOJkElsRsumMcUCUXafsgQug+r2kZF1gDdMcPirC45a7aWhjtJfkYQo2tDGDF1Tb3D/56ih2MpfdWcyB8/yAL2pA63VOuLrZpAnWm8wlyIt7jX19rKj1AQZs3YjvvTtJA=</vt:lpwstr>
-  </property>
-</Properties>
-</file>
-
-<file path=xl\drawings\drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>24130</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>183515</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="194878" name="Picture 1" descr="NOUYA+logo"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="373380"/>
-          <a:ext cx="7620" cy="159385"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>24130</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>183515</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="194879" name="Picture 1" descr="NOUYA+logo"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="373380"/>
-          <a:ext cx="7620" cy="159385"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>24130</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>183515</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="194880" name="Picture 1" descr="NOUYA+logo"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="373380"/>
-          <a:ext cx="7620" cy="159385"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>24130</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>183515</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="194881" name="Picture 1" descr="NOUYA+logo"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="373380"/>
-          <a:ext cx="7620" cy="159385"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>266700</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="194882" name="Picture 1" descr="NOUYA+logo"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="539750"/>
-          <a:ext cx="7620" cy="190500"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>266700</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="194883" name="Picture 1" descr="NOUYA+logo"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="539750"/>
-          <a:ext cx="7620" cy="190500"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>266700</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="194884" name="Picture 1" descr="NOUYA+logo"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="539750"/>
-          <a:ext cx="7620" cy="190500"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>266700</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="194885" name="Picture 1" descr="NOUYA+logo"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="539750"/>
-          <a:ext cx="7620" cy="190500"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>24130</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>183515</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="194886" name="Picture 1" descr="NOUYA+logo"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="373380"/>
-          <a:ext cx="7620" cy="159385"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>24130</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>183515</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="194887" name="Picture 1" descr="NOUYA+logo"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="373380"/>
-          <a:ext cx="7620" cy="159385"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>24130</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>183515</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="194888" name="Picture 1" descr="NOUYA+logo"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="373380"/>
-          <a:ext cx="7620" cy="159385"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>24130</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>183515</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="194889" name="Picture 1" descr="NOUYA+logo"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="373380"/>
-          <a:ext cx="7620" cy="159385"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>266700</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="194890" name="Picture 1" descr="NOUYA+logo"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="539750"/>
-          <a:ext cx="7620" cy="190500"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>266700</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="194891" name="Picture 1" descr="NOUYA+logo"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="539750"/>
-          <a:ext cx="7620" cy="190500"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>266700</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="194892" name="Picture 1" descr="NOUYA+logo"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="539750"/>
-          <a:ext cx="7620" cy="190500"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>266700</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="194893" name="Picture 1" descr="NOUYA+logo"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="539750"/>
-          <a:ext cx="7620" cy="190500"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>24130</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>183515</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="194894" name="Picture 1" descr="NOUYA+logo"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="373380"/>
-          <a:ext cx="7620" cy="159385"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>24130</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>183515</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="194895" name="Picture 1" descr="NOUYA+logo"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="373380"/>
-          <a:ext cx="7620" cy="159385"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>24130</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>183515</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="194896" name="Picture 1" descr="NOUYA+logo"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="373380"/>
-          <a:ext cx="7620" cy="159385"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>24130</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>183515</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="194897" name="Picture 1" descr="NOUYA+logo"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="373380"/>
-          <a:ext cx="7620" cy="159385"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>266700</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="194898" name="Picture 1" descr="NOUYA+logo"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="539750"/>
-          <a:ext cx="7620" cy="190500"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>266700</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="194899" name="Picture 1" descr="NOUYA+logo"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="539750"/>
-          <a:ext cx="7620" cy="190500"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>266700</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="194900" name="Picture 1" descr="NOUYA+logo"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="539750"/>
-          <a:ext cx="7620" cy="190500"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>266700</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="194901" name="Picture 1" descr="NOUYA+logo"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="539750"/>
-          <a:ext cx="7620" cy="190500"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>546100</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>69850</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>95885</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>120015</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="image3"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="5873750" y="69850"/>
-          <a:ext cx="1600835" cy="1542415"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl\drawings\drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>24130</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>183515</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1" descr="NOUYA+logo"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="373380"/>
-          <a:ext cx="7620" cy="159385"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>24130</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>183515</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 1" descr="NOUYA+logo"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="373380"/>
-          <a:ext cx="7620" cy="159385"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>24130</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>183515</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 1" descr="NOUYA+logo"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="373380"/>
-          <a:ext cx="7620" cy="159385"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>24130</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>183515</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Picture 1" descr="NOUYA+logo"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="373380"/>
-          <a:ext cx="7620" cy="159385"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>266700</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="Picture 1" descr="NOUYA+logo"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="539750"/>
-          <a:ext cx="7620" cy="190500"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>266700</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="Picture 1" descr="NOUYA+logo"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="539750"/>
-          <a:ext cx="7620" cy="190500"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>266700</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="Picture 1" descr="NOUYA+logo"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="539750"/>
-          <a:ext cx="7620" cy="190500"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>266700</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="Picture 1" descr="NOUYA+logo"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="539750"/>
-          <a:ext cx="7620" cy="190500"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>24130</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>183515</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="Picture 1" descr="NOUYA+logo"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="373380"/>
-          <a:ext cx="7620" cy="159385"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>24130</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>183515</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="11" name="Picture 1" descr="NOUYA+logo"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="373380"/>
-          <a:ext cx="7620" cy="159385"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>24130</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>183515</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="12" name="Picture 1" descr="NOUYA+logo"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="373380"/>
-          <a:ext cx="7620" cy="159385"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>24130</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>183515</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="13" name="Picture 1" descr="NOUYA+logo"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="373380"/>
-          <a:ext cx="7620" cy="159385"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>266700</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="14" name="Picture 1" descr="NOUYA+logo"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="539750"/>
-          <a:ext cx="7620" cy="190500"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>266700</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="15" name="Picture 1" descr="NOUYA+logo"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="539750"/>
-          <a:ext cx="7620" cy="190500"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>266700</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="16" name="Picture 1" descr="NOUYA+logo"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="539750"/>
-          <a:ext cx="7620" cy="190500"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>266700</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="17" name="Picture 1" descr="NOUYA+logo"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="539750"/>
-          <a:ext cx="7620" cy="190500"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>24130</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>183515</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="18" name="Picture 1" descr="NOUYA+logo"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="373380"/>
-          <a:ext cx="7620" cy="159385"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>24130</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>183515</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="19" name="Picture 1" descr="NOUYA+logo"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="373380"/>
-          <a:ext cx="7620" cy="159385"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>24130</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>183515</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="20" name="Picture 1" descr="NOUYA+logo"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="373380"/>
-          <a:ext cx="7620" cy="159385"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>24130</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>183515</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="21" name="Picture 1" descr="NOUYA+logo"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="373380"/>
-          <a:ext cx="7620" cy="159385"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>266700</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="22" name="Picture 1" descr="NOUYA+logo"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="539750"/>
-          <a:ext cx="7620" cy="190500"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>266700</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="23" name="Picture 1" descr="NOUYA+logo"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="539750"/>
-          <a:ext cx="7620" cy="190500"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>266700</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="24" name="Picture 1" descr="NOUYA+logo"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="539750"/>
-          <a:ext cx="7620" cy="190500"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>266700</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="25" name="Picture 1" descr="NOUYA+logo"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="539750"/>
-          <a:ext cx="7620" cy="190500"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>565150</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>50800</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>213360</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>5080</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="26" name="image3"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="5892800" y="50800"/>
-          <a:ext cx="1699260" cy="1637030"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl\drawings\drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>24130</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>183515</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="190643" name="Picture 1" descr="NOUYA+logo"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="373380"/>
-          <a:ext cx="7620" cy="159385"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>24130</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>183515</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="190644" name="Picture 1" descr="NOUYA+logo"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="373380"/>
-          <a:ext cx="7620" cy="159385"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>24130</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>183515</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="190645" name="Picture 1" descr="NOUYA+logo"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="373380"/>
-          <a:ext cx="7620" cy="159385"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>24130</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>183515</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="190646" name="Picture 1" descr="NOUYA+logo"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="373380"/>
-          <a:ext cx="7620" cy="159385"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>266700</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="190647" name="Picture 1" descr="NOUYA+logo"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="539750"/>
-          <a:ext cx="7620" cy="190500"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>266700</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="190648" name="Picture 1" descr="NOUYA+logo"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="539750"/>
-          <a:ext cx="7620" cy="190500"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>266700</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="190649" name="Picture 1" descr="NOUYA+logo"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="539750"/>
-          <a:ext cx="7620" cy="190500"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>266700</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="190650" name="Picture 1" descr="NOUYA+logo"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="539750"/>
-          <a:ext cx="7620" cy="190500"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>422910</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>107950</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>339090</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>252730</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="image3"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="5558790" y="107950"/>
-          <a:ext cx="1699260" cy="1637030"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl\drawings\drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>24130</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>183515</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="188880" name="Picture 1" descr="NOUYA+logo"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="373380"/>
-          <a:ext cx="7620" cy="159385"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>24130</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>183515</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="188881" name="Picture 1" descr="NOUYA+logo"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="373380"/>
-          <a:ext cx="7620" cy="159385"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>24130</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>183515</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="188882" name="Picture 1" descr="NOUYA+logo"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="373380"/>
-          <a:ext cx="7620" cy="159385"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>24130</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>183515</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="188883" name="Picture 1" descr="NOUYA+logo"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="373380"/>
-          <a:ext cx="7620" cy="159385"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>266700</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="188884" name="Picture 1" descr="NOUYA+logo"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="539750"/>
-          <a:ext cx="7620" cy="190500"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>266700</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="188885" name="Picture 1" descr="NOUYA+logo"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="539750"/>
-          <a:ext cx="7620" cy="190500"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>266700</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="188886" name="Picture 1" descr="NOUYA+logo"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="539750"/>
-          <a:ext cx="7620" cy="190500"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>266700</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="188887" name="Picture 1" descr="NOUYA+logo"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="539750"/>
-          <a:ext cx="7620" cy="190500"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>549910</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>266700</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>179070</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>220980</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="image3"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="5943600" y="266700"/>
-          <a:ext cx="1699260" cy="1637030"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl\drawings\drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>24130</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>183515</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1" descr="NOUYA+logo"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="373380"/>
-          <a:ext cx="7620" cy="159385"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>24130</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>183515</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 1" descr="NOUYA+logo"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="373380"/>
-          <a:ext cx="7620" cy="159385"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>24130</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>183515</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 1" descr="NOUYA+logo"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="373380"/>
-          <a:ext cx="7620" cy="159385"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>24130</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>183515</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Picture 1" descr="NOUYA+logo"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="373380"/>
-          <a:ext cx="7620" cy="159385"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>266700</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="Picture 1" descr="NOUYA+logo"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="539750"/>
-          <a:ext cx="7620" cy="190500"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>266700</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="Picture 1" descr="NOUYA+logo"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="539750"/>
-          <a:ext cx="7620" cy="190500"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>266700</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="Picture 1" descr="NOUYA+logo"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="539750"/>
-          <a:ext cx="7620" cy="190500"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>266700</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="Picture 1" descr="NOUYA+logo"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="539750"/>
-          <a:ext cx="7620" cy="190500"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>24130</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>183515</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="Picture 1" descr="NOUYA+logo"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="373380"/>
-          <a:ext cx="7620" cy="159385"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>24130</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>183515</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="11" name="Picture 1" descr="NOUYA+logo"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="373380"/>
-          <a:ext cx="7620" cy="159385"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>24130</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>183515</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="12" name="Picture 1" descr="NOUYA+logo"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="373380"/>
-          <a:ext cx="7620" cy="159385"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>24130</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>183515</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="13" name="Picture 1" descr="NOUYA+logo"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="373380"/>
-          <a:ext cx="7620" cy="159385"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>266700</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="14" name="Picture 1" descr="NOUYA+logo"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="539750"/>
-          <a:ext cx="7620" cy="190500"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>266700</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="15" name="Picture 1" descr="NOUYA+logo"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="539750"/>
-          <a:ext cx="7620" cy="190500"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>266700</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="16" name="Picture 1" descr="NOUYA+logo"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="539750"/>
-          <a:ext cx="7620" cy="190500"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>266700</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="17" name="Picture 1" descr="NOUYA+logo"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="539750"/>
-          <a:ext cx="7620" cy="190500"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>76835</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>635</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>541655</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>145415</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="18" name="image3"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="5878195" y="635"/>
-          <a:ext cx="1699260" cy="1637030"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl\drawings\drawing6.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>24130</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>183515</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1" descr="NOUYA+logo"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="373380"/>
-          <a:ext cx="7620" cy="159385"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>24130</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>183515</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 1" descr="NOUYA+logo"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="373380"/>
-          <a:ext cx="7620" cy="159385"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>24130</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>183515</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 1" descr="NOUYA+logo"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="373380"/>
-          <a:ext cx="7620" cy="159385"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>24130</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>183515</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Picture 1" descr="NOUYA+logo"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="373380"/>
-          <a:ext cx="7620" cy="159385"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>266700</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="Picture 1" descr="NOUYA+logo"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="539750"/>
-          <a:ext cx="7620" cy="190500"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>266700</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="Picture 1" descr="NOUYA+logo"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="539750"/>
-          <a:ext cx="7620" cy="190500"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>266700</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="Picture 1" descr="NOUYA+logo"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="539750"/>
-          <a:ext cx="7620" cy="190500"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>266700</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="Picture 1" descr="NOUYA+logo"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="539750"/>
-          <a:ext cx="7620" cy="190500"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>510540</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>635</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>452120</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>145415</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="image3"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="5646420" y="635"/>
-          <a:ext cx="1699260" cy="1637030"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl\drawings\drawing7.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>24130</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>183515</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1" descr="NOUYA+logo"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="373380"/>
-          <a:ext cx="7620" cy="159385"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>24130</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>183515</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 1" descr="NOUYA+logo"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="373380"/>
-          <a:ext cx="7620" cy="159385"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>24130</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>183515</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 1" descr="NOUYA+logo"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="373380"/>
-          <a:ext cx="7620" cy="159385"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>24130</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>183515</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Picture 1" descr="NOUYA+logo"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="373380"/>
-          <a:ext cx="7620" cy="159385"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>266700</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="Picture 1" descr="NOUYA+logo"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="539750"/>
-          <a:ext cx="7620" cy="190500"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>266700</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="Picture 1" descr="NOUYA+logo"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="539750"/>
-          <a:ext cx="7620" cy="190500"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>266700</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="Picture 1" descr="NOUYA+logo"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="539750"/>
-          <a:ext cx="7620" cy="190500"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>266700</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="Picture 1" descr="NOUYA+logo"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="539750"/>
-          <a:ext cx="7620" cy="190500"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>373380</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>158750</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>152400</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>163830</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="image3"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="5600700" y="158750"/>
-          <a:ext cx="1699260" cy="1637030"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl\drawings\drawing8.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>24130</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>183515</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1" descr="NOUYA+logo"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="373380"/>
-          <a:ext cx="7620" cy="159385"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>24130</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>183515</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 1" descr="NOUYA+logo"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="373380"/>
-          <a:ext cx="7620" cy="159385"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>24130</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>183515</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 1" descr="NOUYA+logo"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="373380"/>
-          <a:ext cx="7620" cy="159385"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>24130</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>183515</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Picture 1" descr="NOUYA+logo"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="373380"/>
-          <a:ext cx="7620" cy="159385"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>266700</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="Picture 1" descr="NOUYA+logo"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="539750"/>
-          <a:ext cx="7620" cy="190500"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>266700</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="Picture 1" descr="NOUYA+logo"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="539750"/>
-          <a:ext cx="7620" cy="190500"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>266700</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="Picture 1" descr="NOUYA+logo"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="539750"/>
-          <a:ext cx="7620" cy="190500"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>266700</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="Picture 1" descr="NOUYA+logo"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="539750"/>
-          <a:ext cx="7620" cy="190500"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>302260</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>127000</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>570230</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>81915</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="image3"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="5384800" y="127000"/>
-          <a:ext cx="1502410" cy="1447165"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl\sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1720" uniqueCount="137">
   <si>
     <t>NOUYA南亚新材料科技股份有限公司</t>
@@ -5065,7 +519,7 @@
 </sst>
 </file>
 
-<file path=xl\styles.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="14">
     <numFmt numFmtId="26" formatCode="\$#,##0.00_);[Red]\(\$#,##0.00\)"/>
@@ -6330,7 +1784,4543 @@
 </styleSheet>
 </file>
 
-<file path=xl\theme\theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>24130</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>183515</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="194878" name="Picture 1" descr="NOUYA+logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="373380"/>
+          <a:ext cx="7620" cy="159385"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>24130</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>183515</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="194879" name="Picture 1" descr="NOUYA+logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="373380"/>
+          <a:ext cx="7620" cy="159385"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>24130</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>183515</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="194880" name="Picture 1" descr="NOUYA+logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="373380"/>
+          <a:ext cx="7620" cy="159385"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>24130</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>183515</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="194881" name="Picture 1" descr="NOUYA+logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="373380"/>
+          <a:ext cx="7620" cy="159385"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>266700</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="194882" name="Picture 1" descr="NOUYA+logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="539750"/>
+          <a:ext cx="7620" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>266700</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="194883" name="Picture 1" descr="NOUYA+logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="539750"/>
+          <a:ext cx="7620" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>266700</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="194884" name="Picture 1" descr="NOUYA+logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="539750"/>
+          <a:ext cx="7620" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>266700</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="194885" name="Picture 1" descr="NOUYA+logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="539750"/>
+          <a:ext cx="7620" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>24130</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>183515</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="194886" name="Picture 1" descr="NOUYA+logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="373380"/>
+          <a:ext cx="7620" cy="159385"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>24130</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>183515</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="194887" name="Picture 1" descr="NOUYA+logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="373380"/>
+          <a:ext cx="7620" cy="159385"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>24130</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>183515</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="194888" name="Picture 1" descr="NOUYA+logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="373380"/>
+          <a:ext cx="7620" cy="159385"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>24130</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>183515</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="194889" name="Picture 1" descr="NOUYA+logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="373380"/>
+          <a:ext cx="7620" cy="159385"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>266700</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="194890" name="Picture 1" descr="NOUYA+logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="539750"/>
+          <a:ext cx="7620" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>266700</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="194891" name="Picture 1" descr="NOUYA+logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="539750"/>
+          <a:ext cx="7620" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>266700</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="194892" name="Picture 1" descr="NOUYA+logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="539750"/>
+          <a:ext cx="7620" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>266700</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="194893" name="Picture 1" descr="NOUYA+logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="539750"/>
+          <a:ext cx="7620" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>24130</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>183515</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="194894" name="Picture 1" descr="NOUYA+logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="373380"/>
+          <a:ext cx="7620" cy="159385"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>24130</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>183515</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="194895" name="Picture 1" descr="NOUYA+logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="373380"/>
+          <a:ext cx="7620" cy="159385"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>24130</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>183515</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="194896" name="Picture 1" descr="NOUYA+logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="373380"/>
+          <a:ext cx="7620" cy="159385"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>24130</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>183515</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="194897" name="Picture 1" descr="NOUYA+logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="373380"/>
+          <a:ext cx="7620" cy="159385"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>266700</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="194898" name="Picture 1" descr="NOUYA+logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="539750"/>
+          <a:ext cx="7620" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>266700</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="194899" name="Picture 1" descr="NOUYA+logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="539750"/>
+          <a:ext cx="7620" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>266700</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="194900" name="Picture 1" descr="NOUYA+logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="539750"/>
+          <a:ext cx="7620" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>266700</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="194901" name="Picture 1" descr="NOUYA+logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="539750"/>
+          <a:ext cx="7620" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>546100</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>69850</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>95885</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>120015</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="image3"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5873750" y="69850"/>
+          <a:ext cx="1600835" cy="1542415"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>24130</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>183515</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1" descr="NOUYA+logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="373380"/>
+          <a:ext cx="7620" cy="159385"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>24130</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>183515</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 1" descr="NOUYA+logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="373380"/>
+          <a:ext cx="7620" cy="159385"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>24130</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>183515</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 1" descr="NOUYA+logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="373380"/>
+          <a:ext cx="7620" cy="159385"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>24130</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>183515</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 1" descr="NOUYA+logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="373380"/>
+          <a:ext cx="7620" cy="159385"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>266700</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Picture 1" descr="NOUYA+logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="539750"/>
+          <a:ext cx="7620" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>266700</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Picture 1" descr="NOUYA+logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="539750"/>
+          <a:ext cx="7620" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>266700</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Picture 1" descr="NOUYA+logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="539750"/>
+          <a:ext cx="7620" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>266700</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="Picture 1" descr="NOUYA+logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="539750"/>
+          <a:ext cx="7620" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>24130</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>183515</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="Picture 1" descr="NOUYA+logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="373380"/>
+          <a:ext cx="7620" cy="159385"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>24130</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>183515</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="Picture 1" descr="NOUYA+logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="373380"/>
+          <a:ext cx="7620" cy="159385"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>24130</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>183515</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="Picture 1" descr="NOUYA+logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="373380"/>
+          <a:ext cx="7620" cy="159385"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>24130</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>183515</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="Picture 1" descr="NOUYA+logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="373380"/>
+          <a:ext cx="7620" cy="159385"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>266700</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="14" name="Picture 1" descr="NOUYA+logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="539750"/>
+          <a:ext cx="7620" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>266700</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="15" name="Picture 1" descr="NOUYA+logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="539750"/>
+          <a:ext cx="7620" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>266700</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="16" name="Picture 1" descr="NOUYA+logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="539750"/>
+          <a:ext cx="7620" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>266700</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="17" name="Picture 1" descr="NOUYA+logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="539750"/>
+          <a:ext cx="7620" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>24130</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>183515</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="18" name="Picture 1" descr="NOUYA+logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="373380"/>
+          <a:ext cx="7620" cy="159385"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>24130</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>183515</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="19" name="Picture 1" descr="NOUYA+logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="373380"/>
+          <a:ext cx="7620" cy="159385"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>24130</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>183515</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="20" name="Picture 1" descr="NOUYA+logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="373380"/>
+          <a:ext cx="7620" cy="159385"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>24130</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>183515</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="21" name="Picture 1" descr="NOUYA+logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="373380"/>
+          <a:ext cx="7620" cy="159385"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>266700</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="22" name="Picture 1" descr="NOUYA+logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="539750"/>
+          <a:ext cx="7620" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>266700</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="23" name="Picture 1" descr="NOUYA+logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="539750"/>
+          <a:ext cx="7620" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>266700</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="24" name="Picture 1" descr="NOUYA+logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="539750"/>
+          <a:ext cx="7620" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>266700</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="25" name="Picture 1" descr="NOUYA+logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="539750"/>
+          <a:ext cx="7620" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>565150</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>50800</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>213360</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>5080</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="26" name="image3"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5892800" y="50800"/>
+          <a:ext cx="1699260" cy="1637030"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>24130</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>183515</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="190643" name="Picture 1" descr="NOUYA+logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="373380"/>
+          <a:ext cx="7620" cy="159385"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>24130</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>183515</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="190644" name="Picture 1" descr="NOUYA+logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="373380"/>
+          <a:ext cx="7620" cy="159385"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>24130</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>183515</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="190645" name="Picture 1" descr="NOUYA+logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="373380"/>
+          <a:ext cx="7620" cy="159385"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>24130</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>183515</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="190646" name="Picture 1" descr="NOUYA+logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="373380"/>
+          <a:ext cx="7620" cy="159385"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>266700</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="190647" name="Picture 1" descr="NOUYA+logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="539750"/>
+          <a:ext cx="7620" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>266700</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="190648" name="Picture 1" descr="NOUYA+logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="539750"/>
+          <a:ext cx="7620" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>266700</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="190649" name="Picture 1" descr="NOUYA+logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="539750"/>
+          <a:ext cx="7620" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>266700</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="190650" name="Picture 1" descr="NOUYA+logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="539750"/>
+          <a:ext cx="7620" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>422910</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>107950</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>339090</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>252730</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="image3"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5558790" y="107950"/>
+          <a:ext cx="1699260" cy="1637030"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>24130</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>183515</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="188880" name="Picture 1" descr="NOUYA+logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="373380"/>
+          <a:ext cx="7620" cy="159385"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>24130</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>183515</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="188881" name="Picture 1" descr="NOUYA+logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="373380"/>
+          <a:ext cx="7620" cy="159385"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>24130</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>183515</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="188882" name="Picture 1" descr="NOUYA+logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="373380"/>
+          <a:ext cx="7620" cy="159385"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>24130</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>183515</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="188883" name="Picture 1" descr="NOUYA+logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="373380"/>
+          <a:ext cx="7620" cy="159385"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>266700</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="188884" name="Picture 1" descr="NOUYA+logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="539750"/>
+          <a:ext cx="7620" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>266700</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="188885" name="Picture 1" descr="NOUYA+logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="539750"/>
+          <a:ext cx="7620" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>266700</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="188886" name="Picture 1" descr="NOUYA+logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="539750"/>
+          <a:ext cx="7620" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>266700</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="188887" name="Picture 1" descr="NOUYA+logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="539750"/>
+          <a:ext cx="7620" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>549910</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>266700</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>179070</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>220980</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="image3"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5943600" y="266700"/>
+          <a:ext cx="1699260" cy="1637030"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>24130</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>183515</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1" descr="NOUYA+logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="373380"/>
+          <a:ext cx="7620" cy="159385"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>24130</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>183515</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 1" descr="NOUYA+logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="373380"/>
+          <a:ext cx="7620" cy="159385"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>24130</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>183515</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 1" descr="NOUYA+logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="373380"/>
+          <a:ext cx="7620" cy="159385"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>24130</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>183515</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 1" descr="NOUYA+logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="373380"/>
+          <a:ext cx="7620" cy="159385"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>266700</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Picture 1" descr="NOUYA+logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="539750"/>
+          <a:ext cx="7620" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>266700</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Picture 1" descr="NOUYA+logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="539750"/>
+          <a:ext cx="7620" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>266700</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Picture 1" descr="NOUYA+logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="539750"/>
+          <a:ext cx="7620" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>266700</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="Picture 1" descr="NOUYA+logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="539750"/>
+          <a:ext cx="7620" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>24130</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>183515</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="Picture 1" descr="NOUYA+logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="373380"/>
+          <a:ext cx="7620" cy="159385"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>24130</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>183515</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="Picture 1" descr="NOUYA+logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="373380"/>
+          <a:ext cx="7620" cy="159385"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>24130</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>183515</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="Picture 1" descr="NOUYA+logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="373380"/>
+          <a:ext cx="7620" cy="159385"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>24130</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>183515</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="Picture 1" descr="NOUYA+logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="373380"/>
+          <a:ext cx="7620" cy="159385"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>266700</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="14" name="Picture 1" descr="NOUYA+logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="539750"/>
+          <a:ext cx="7620" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>266700</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="15" name="Picture 1" descr="NOUYA+logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="539750"/>
+          <a:ext cx="7620" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>266700</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="16" name="Picture 1" descr="NOUYA+logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="539750"/>
+          <a:ext cx="7620" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>266700</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="17" name="Picture 1" descr="NOUYA+logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="539750"/>
+          <a:ext cx="7620" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>76835</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>635</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>541655</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>145415</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="18" name="image3"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5878195" y="635"/>
+          <a:ext cx="1699260" cy="1637030"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>24130</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>183515</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1" descr="NOUYA+logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="373380"/>
+          <a:ext cx="7620" cy="159385"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>24130</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>183515</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 1" descr="NOUYA+logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="373380"/>
+          <a:ext cx="7620" cy="159385"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>24130</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>183515</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 1" descr="NOUYA+logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="373380"/>
+          <a:ext cx="7620" cy="159385"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>24130</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>183515</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 1" descr="NOUYA+logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="373380"/>
+          <a:ext cx="7620" cy="159385"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>266700</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Picture 1" descr="NOUYA+logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="539750"/>
+          <a:ext cx="7620" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>266700</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Picture 1" descr="NOUYA+logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="539750"/>
+          <a:ext cx="7620" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>266700</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Picture 1" descr="NOUYA+logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="539750"/>
+          <a:ext cx="7620" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>266700</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="Picture 1" descr="NOUYA+logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="539750"/>
+          <a:ext cx="7620" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>510540</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>635</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>452120</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>145415</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="image3"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5646420" y="635"/>
+          <a:ext cx="1699260" cy="1637030"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>24130</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>183515</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1" descr="NOUYA+logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="373380"/>
+          <a:ext cx="7620" cy="159385"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>24130</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>183515</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 1" descr="NOUYA+logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="373380"/>
+          <a:ext cx="7620" cy="159385"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>24130</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>183515</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 1" descr="NOUYA+logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="373380"/>
+          <a:ext cx="7620" cy="159385"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>24130</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>183515</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 1" descr="NOUYA+logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="373380"/>
+          <a:ext cx="7620" cy="159385"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>266700</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Picture 1" descr="NOUYA+logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="539750"/>
+          <a:ext cx="7620" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>266700</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Picture 1" descr="NOUYA+logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="539750"/>
+          <a:ext cx="7620" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>266700</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Picture 1" descr="NOUYA+logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="539750"/>
+          <a:ext cx="7620" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>266700</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="Picture 1" descr="NOUYA+logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="539750"/>
+          <a:ext cx="7620" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>373380</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>158750</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>163830</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="image3"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5600700" y="158750"/>
+          <a:ext cx="1699260" cy="1637030"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>24130</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>183515</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1" descr="NOUYA+logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="373380"/>
+          <a:ext cx="7620" cy="159385"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>24130</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>183515</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 1" descr="NOUYA+logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="373380"/>
+          <a:ext cx="7620" cy="159385"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>24130</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>183515</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 1" descr="NOUYA+logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="373380"/>
+          <a:ext cx="7620" cy="159385"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>24130</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>183515</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 1" descr="NOUYA+logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="373380"/>
+          <a:ext cx="7620" cy="159385"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>266700</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Picture 1" descr="NOUYA+logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="539750"/>
+          <a:ext cx="7620" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>266700</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Picture 1" descr="NOUYA+logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="539750"/>
+          <a:ext cx="7620" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>266700</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Picture 1" descr="NOUYA+logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="539750"/>
+          <a:ext cx="7620" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>266700</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="Picture 1" descr="NOUYA+logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="539750"/>
+          <a:ext cx="7620" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>302260</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>570230</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>81915</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="image3"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5384800" y="127000"/>
+          <a:ext cx="1502410" cy="1447165"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
     <a:clrScheme name="Office">
@@ -6585,52 +6575,7 @@
 </a:theme>
 </file>
 
-<file path=xl\workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr/>
-  <bookViews>
-    <workbookView windowWidth="20750" windowHeight="10270" activeTab="4"/>
-  </bookViews>
-  <sheets>
-    <sheet name="NY2170H" sheetId="13" r:id="rId1"/>
-    <sheet name="NY3170HF" sheetId="16" r:id="rId2"/>
-    <sheet name="NY3170M" sheetId="7" r:id="rId3"/>
-    <sheet name="NY3170M2" sheetId="8" r:id="rId4"/>
-    <sheet name="NY2150" sheetId="17" r:id="rId5"/>
-    <sheet name="NY3150HF" sheetId="18" r:id="rId6"/>
-    <sheet name="NY3176HF" sheetId="19" r:id="rId7"/>
-    <sheet name="NY6300SN" sheetId="20" r:id="rId8"/>
-  </sheets>
-  <definedNames>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">NY2170H!$1:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="2">NY3170M!$1:$8</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="3">NY3170M2!$1:$9</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">NY2170H!$A$1:$L$75</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">NY3170M!$A$1:$L$112</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="1">NY3170HF!$1:$9</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">NY3170HF!$A$1:$L$83</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'NY2150'!$A$1:$K$69</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">NY3150HF!$A$1:$L$90</definedName>
-  </definedNames>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
-</workbook>
-</file>
-
-<file path=xl\worksheets\sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
@@ -9069,7 +9014,7 @@
 </worksheet>
 </file>
 
-<file path=xl\worksheets\sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
@@ -11799,7 +11744,7 @@
 </worksheet>
 </file>
 
-<file path=xl\worksheets\sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
@@ -15606,7 +15551,7 @@
 </worksheet>
 </file>
 
-<file path=xl\worksheets\sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:K93"/>
@@ -18691,7 +18636,7 @@
 </worksheet>
 </file>
 
-<file path=xl\worksheets\sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:P69"/>
@@ -21042,7 +20987,7 @@
 </worksheet>
 </file>
 
-<file path=xl\worksheets\sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:K90"/>
@@ -23961,7 +23906,7 @@
 </worksheet>
 </file>
 
-<file path=xl\worksheets\sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:K33"/>
@@ -24676,7 +24621,7 @@
 </worksheet>
 </file>
 
-<file path=xl\worksheets\sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:K40"/>
